--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,12 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520922.2441249581</v>
+        <v>520922</v>
       </c>
       <c r="R6" t="n">
-        <v>6364296.395722182</v>
+        <v>6364296</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1249,19 +1244,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1305,12 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520922.2441249581</v>
+        <v>520922</v>
       </c>
       <c r="R7" t="n">
-        <v>6364296.395722182</v>
+        <v>6364296</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1375,19 +1355,9 @@
           <t>1989-06-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1989-06-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1431,12 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520923.8363422108</v>
+        <v>520924</v>
       </c>
       <c r="R8" t="n">
-        <v>6364196.243651968</v>
+        <v>6364196</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1501,19 +1466,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1557,12 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520923.8363422108</v>
+        <v>520924</v>
       </c>
       <c r="R9" t="n">
-        <v>6364196.243651968</v>
+        <v>6364196</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1627,19 +1577,9 @@
           <t>1992-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110337</v>
+        <v>110346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101877</v>
+        <v>101883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110346</v>
+        <v>110351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101883</v>
+        <v>101884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110351</v>
+        <v>110379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101884</v>
+        <v>101911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110379</v>
+        <v>110385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101911</v>
+        <v>101917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110385</v>
+        <v>110392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101917</v>
+        <v>101924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110392</v>
+        <v>110396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101924</v>
+        <v>101928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110396</v>
+        <v>110404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101928</v>
+        <v>101935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110407</v>
+        <v>110412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101938</v>
+        <v>101943</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110412</v>
+        <v>110420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101943</v>
+        <v>101951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>73967111</v>
       </c>
       <c r="B6" t="n">
-        <v>110420</v>
+        <v>110430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>74268555</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>74567114</v>
       </c>
       <c r="B8" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>75157951</v>
       </c>
       <c r="B9" t="n">
-        <v>101951</v>
+        <v>101961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74567114</v>
+        <v>135163657</v>
       </c>
       <c r="B2" t="n">
-        <v>99142</v>
+        <v>107949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>34 1992 Germunderyd 400 m SV, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520924</v>
+        <v>520623</v>
       </c>
       <c r="R2" t="n">
-        <v>6364196</v>
+        <v>6364349</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Listera ovata. LEG: Folke Jacobsson. KOM: Det. GS+ MLN,ABC,FkJ</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,35 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109865443</v>
+        <v>135164181</v>
       </c>
       <c r="B3" t="n">
-        <v>110078</v>
+        <v>107693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>1897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,20 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520683</v>
+        <v>520193</v>
       </c>
       <c r="R3" t="n">
-        <v>6364308</v>
+        <v>6364512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,52 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83270201</v>
+        <v>74567114</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Germunderyd, Sm</t>
+          <t>34 1992 Germunderyd 400 m SV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521131</v>
+        <v>520924</v>
       </c>
       <c r="R4" t="n">
-        <v>6364376</v>
+        <v>6364196</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,19 +932,19 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>DCC43D0C-A4D2-4AC7-A341-0A6C94D01BC3</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Listera ovata. LEG: Folke Jacobsson. KOM: Det. GS+ MLN,ABC,FkJ</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,72 +955,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83270202</v>
+        <v>135164666</v>
       </c>
       <c r="B5" t="n">
-        <v>106813</v>
+        <v>108205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>220083</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521144</v>
+        <v>519896</v>
       </c>
       <c r="R5" t="n">
-        <v>6364387</v>
+        <v>6364351</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,19 +1043,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>489F90CB-D8B3-4A66-BE03-FA732200F684</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,43 +1065,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83270419</v>
+        <v>135164819</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>109947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1136,24 +1105,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521021</v>
+        <v>519881</v>
       </c>
       <c r="R6" t="n">
-        <v>6364455</v>
+        <v>6364390</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1140,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>61565E2B-D31C-40FB-8225-58A31A9ADCF4</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,43 +1162,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83270420</v>
+        <v>109865443</v>
       </c>
       <c r="B7" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1246,24 +1202,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521050</v>
+        <v>520683</v>
       </c>
       <c r="R7" t="n">
-        <v>6364351</v>
+        <v>6364308</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,19 +1241,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5A1585F4-19CD-4532-B8DA-30E03A2134D8</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,49 +1257,46 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109865441</v>
+        <v>83270201</v>
       </c>
       <c r="B8" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1356,24 +1304,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520683</v>
+        <v>521131</v>
       </c>
       <c r="R8" t="n">
-        <v>6364308</v>
+        <v>6364376</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,14 +1343,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>DCC43D0C-A4D2-4AC7-A341-0A6C94D01BC3</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,71 +1364,74 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Marielle Gustafsson, Monika Mörk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95196552</v>
+        <v>83270202</v>
       </c>
       <c r="B9" t="n">
-        <v>102225</v>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521230</v>
+        <v>521144</v>
       </c>
       <c r="R9" t="n">
-        <v>6364408</v>
+        <v>6364387</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,14 +1453,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>489F90CB-D8B3-4A66-BE03-FA732200F684</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-30</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-30</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,51 +1474,49 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Marielle Gustafsson, Monika Mörk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75157951</v>
+        <v>83270419</v>
       </c>
       <c r="B10" t="n">
-        <v>102442</v>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221333</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1565,20 +1524,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Germunderyd 400 m SV, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520924</v>
+        <v>521021</v>
       </c>
       <c r="R10" t="n">
-        <v>6364196</v>
+        <v>6364455</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,19 +1563,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>61565E2B-D31C-40FB-8225-58A31A9ADCF4</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Trifolium montanum. LEG: Folke Jacobsson</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,52 +1586,47 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Marielle Gustafsson, Monika Mörk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4793801</v>
+        <v>83270420</v>
       </c>
       <c r="B11" t="n">
-        <v>99879</v>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1676,20 +1634,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Germunderyd Torsgården, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520928</v>
+        <v>521050</v>
       </c>
       <c r="R11" t="n">
-        <v>6364301</v>
+        <v>6364351</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,17 +1675,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>F-Vet-0610</t>
+          <t>5A1585F4-19CD-4532-B8DA-30E03A2134D8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,52 +1696,47 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Marielle Gustafsson, Monika Mörk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74268555</v>
+        <v>109865441</v>
       </c>
       <c r="B12" t="n">
-        <v>99878</v>
+        <v>106156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222361</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1788,19 +1745,23 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Germunderyd Torsgården, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520922</v>
+        <v>520683</v>
       </c>
       <c r="R12" t="n">
-        <v>6364296</v>
+        <v>6364308</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,17 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Carex pulicaris. LEG: Tomas Fasth</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,59 +1799,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109865542</v>
+        <v>95196552</v>
       </c>
       <c r="B13" t="n">
-        <v>104628</v>
+        <v>102225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>221223</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520179</v>
+        <v>521230</v>
       </c>
       <c r="R13" t="n">
-        <v>6364511</v>
+        <v>6364408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,12 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,6 +1904,11 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1972,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73967111</v>
+        <v>75157951</v>
       </c>
       <c r="B14" t="n">
-        <v>111018</v>
+        <v>102442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,16 +1936,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222776</v>
+        <v>221333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2003,14 +1956,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>28 Germunderyd S gdn 200 m VNV, Sm</t>
+          <t>Germunderyd 400 m SV, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520922</v>
+        <v>520924</v>
       </c>
       <c r="R14" t="n">
-        <v>6364296</v>
+        <v>6364196</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2037,17 +1990,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Adoxa moschatellina. LEG: Göran Svensson,  Maja-Lena Nilsson,  Anna-Brita Carlander</t>
+          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Trifolium montanum. LEG: Folke Jacobsson</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2014,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beteshage vid bäck</t>
+          <t>Hagmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2083,47 +2036,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67558320</v>
+        <v>135164446</v>
       </c>
       <c r="B15" t="n">
-        <v>104641</v>
+        <v>107695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224416</v>
+        <v>221705</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520554</v>
+        <v>519987</v>
       </c>
       <c r="R15" t="n">
-        <v>6364402</v>
+        <v>6364423</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2147,12 +2101,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,6 +2130,630 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4793801</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Germunderyd Torsgården, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>520928</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6364301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>F-Vet-0610</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74268555</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99878</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Germunderyd Torsgården, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>520922</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6364296</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Carex pulicaris. LEG: Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>109865542</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>520179</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6364511</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73967111</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111018</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>28 Germunderyd S gdn 200 m VNV, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>520922</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6364296</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Adoxa moschatellina. LEG: Göran Svensson,  Maja-Lena Nilsson,  Anna-Brita Carlander</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Beteshage vid bäck</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>67558320</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>520554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6364402</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135164415</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104720</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>519987</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6364423</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135163657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74567114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164666</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109865443</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83270201</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83270202</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83270419</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83270420</t>
         </is>
       </c>
     </row>
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109865441</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95196552</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75157951</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164446</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2241,6 +2316,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4793801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74268555</t>
         </is>
       </c>
     </row>
@@ -2454,6 +2539,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109865542</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73967111</t>
         </is>
       </c>
     </row>
@@ -2661,6 +2756,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67558320</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2754,8 +2854,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135163657</v>
       </c>
       <c r="B2" t="n">
-        <v>107949</v>
+        <v>108004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135164181</v>
       </c>
       <c r="B3" t="n">
-        <v>107693</v>
+        <v>107748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>135164666</v>
       </c>
       <c r="B5" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135164819</v>
       </c>
       <c r="B6" t="n">
-        <v>109947</v>
+        <v>110003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135164446</v>
       </c>
       <c r="B15" t="n">
-        <v>107695</v>
+        <v>107750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135164415</v>
       </c>
       <c r="B21" t="n">
-        <v>104720</v>
+        <v>104774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135163657</v>
       </c>
       <c r="B2" t="n">
-        <v>108004</v>
+        <v>108031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135164181</v>
       </c>
       <c r="B3" t="n">
-        <v>107748</v>
+        <v>107775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>135164666</v>
       </c>
       <c r="B5" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135164819</v>
       </c>
       <c r="B6" t="n">
-        <v>110003</v>
+        <v>110030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135164446</v>
       </c>
       <c r="B15" t="n">
-        <v>107750</v>
+        <v>107777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135164415</v>
       </c>
       <c r="B21" t="n">
-        <v>104774</v>
+        <v>104801</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74567114</v>
+        <v>135163657</v>
       </c>
       <c r="B2" t="n">
-        <v>99142</v>
+        <v>108036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>34 1992 Germunderyd 400 m SV, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520924</v>
+        <v>520623</v>
       </c>
       <c r="R2" t="n">
-        <v>6364196</v>
+        <v>6364349</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Listera ovata. LEG: Folke Jacobsson. KOM: Det. GS+ MLN,ABC,FkJ</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,40 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74567114</t>
+          <t>https://artportalen.se/Sighting/135163657</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109865443</v>
+        <v>135164181</v>
       </c>
       <c r="B3" t="n">
-        <v>110078</v>
+        <v>107780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>1897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,20 +811,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520683</v>
+        <v>520193</v>
       </c>
       <c r="R3" t="n">
-        <v>6364308</v>
+        <v>6364512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,58 +878,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109865443</t>
+          <t>https://artportalen.se/Sighting/135164181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83270201</v>
+        <v>74567114</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Germunderyd, Sm</t>
+          <t>34 1992 Germunderyd 400 m SV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521131</v>
+        <v>520924</v>
       </c>
       <c r="R4" t="n">
-        <v>6364376</v>
+        <v>6364196</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,19 +947,19 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>DCC43D0C-A4D2-4AC7-A341-0A6C94D01BC3</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Listera ovata. LEG: Folke Jacobsson. KOM: Det. GS+ MLN,ABC,FkJ</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,77 +970,78 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83270201</t>
+          <t>https://artportalen.se/Sighting/74567114</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83270202</v>
+        <v>135164666</v>
       </c>
       <c r="B5" t="n">
-        <v>106813</v>
+        <v>108292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>220083</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521144</v>
+        <v>519896</v>
       </c>
       <c r="R5" t="n">
-        <v>6364387</v>
+        <v>6364351</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,19 +1063,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>489F90CB-D8B3-4A66-BE03-FA732200F684</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,48 +1085,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83270202</t>
+          <t>https://artportalen.se/Sighting/135164666</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83270419</v>
+        <v>135164819</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>110035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1161,24 +1130,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521021</v>
+        <v>519881</v>
       </c>
       <c r="R6" t="n">
-        <v>6364455</v>
+        <v>6364390</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1165,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>61565E2B-D31C-40FB-8225-58A31A9ADCF4</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,48 +1187,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83270419</t>
+          <t>https://artportalen.se/Sighting/135164819</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83270420</v>
+        <v>109865443</v>
       </c>
       <c r="B7" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,24 +1232,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521050</v>
+        <v>520683</v>
       </c>
       <c r="R7" t="n">
-        <v>6364351</v>
+        <v>6364308</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,19 +1271,14 @@
           <t>Alseda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5A1585F4-19CD-4532-B8DA-30E03A2134D8</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-12-19</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,54 +1287,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Monika Mörk</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83270420</t>
+          <t>https://artportalen.se/Sighting/109865443</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109865441</v>
+        <v>83270201</v>
       </c>
       <c r="B8" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1391,24 +1339,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520683</v>
+        <v>521131</v>
       </c>
       <c r="R8" t="n">
-        <v>6364308</v>
+        <v>6364376</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,14 +1378,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>DCC43D0C-A4D2-4AC7-A341-0A6C94D01BC3</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,76 +1399,79 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Marielle Gustafsson, Monika Mörk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109865441</t>
+          <t>https://artportalen.se/Sighting/83270201</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95196552</v>
+        <v>83270202</v>
       </c>
       <c r="B9" t="n">
-        <v>102225</v>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521230</v>
+        <v>521144</v>
       </c>
       <c r="R9" t="n">
-        <v>6364408</v>
+        <v>6364387</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,14 +1493,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>489F90CB-D8B3-4A66-BE03-FA732200F684</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-30</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-30</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,56 +1514,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Marielle Gustafsson, Monika Mörk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95196552</t>
+          <t>https://artportalen.se/Sighting/83270202</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75157951</v>
+        <v>83270419</v>
       </c>
       <c r="B10" t="n">
-        <v>102442</v>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221333</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1610,20 +1569,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Germunderyd 400 m SV, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520924</v>
+        <v>521021</v>
       </c>
       <c r="R10" t="n">
-        <v>6364196</v>
+        <v>6364455</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,19 +1608,19 @@
           <t>Alseda</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>61565E2B-D31C-40FB-8225-58A31A9ADCF4</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Trifolium montanum. LEG: Folke Jacobsson</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,57 +1631,52 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Hagmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Marielle Gustafsson, Monika Mörk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75157951</t>
+          <t>https://artportalen.se/Sighting/83270419</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4793801</v>
+        <v>83270420</v>
       </c>
       <c r="B11" t="n">
-        <v>99879</v>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1726,20 +1684,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Germunderyd Torsgården, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520928</v>
+        <v>521050</v>
       </c>
       <c r="R11" t="n">
-        <v>6364301</v>
+        <v>6364351</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,17 +1725,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>F-Vet-0610</t>
+          <t>5A1585F4-19CD-4532-B8DA-30E03A2134D8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2006-12-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,57 +1746,52 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Marielle Gustafsson, Monika Mörk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4793801</t>
+          <t>https://artportalen.se/Sighting/83270420</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74268555</v>
+        <v>109865441</v>
       </c>
       <c r="B12" t="n">
-        <v>99878</v>
+        <v>106156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222361</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1843,19 +1800,23 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Germunderyd Torsgården, Sm</t>
+          <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520922</v>
+        <v>520683</v>
       </c>
       <c r="R12" t="n">
-        <v>6364296</v>
+        <v>6364308</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,17 +1840,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-06-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Carex pulicaris. LEG: Tomas Fasth</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,64 +1854,56 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74268555</t>
+          <t>https://artportalen.se/Sighting/109865441</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109865542</v>
+        <v>95196552</v>
       </c>
       <c r="B13" t="n">
-        <v>104628</v>
+        <v>102225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>221223</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520179</v>
+        <v>521230</v>
       </c>
       <c r="R13" t="n">
-        <v>6364511</v>
+        <v>6364408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,12 +1947,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,6 +1965,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2031,16 +1984,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109865542</t>
+          <t>https://artportalen.se/Sighting/95196552</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73967111</v>
+        <v>75157951</v>
       </c>
       <c r="B14" t="n">
-        <v>111018</v>
+        <v>102442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,16 +2001,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222776</v>
+        <v>221333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2068,14 +2021,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>28 Germunderyd S gdn 200 m VNV, Sm</t>
+          <t>Germunderyd 400 m SV, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520922</v>
+        <v>520924</v>
       </c>
       <c r="R14" t="n">
-        <v>6364296</v>
+        <v>6364196</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2102,17 +2055,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Adoxa moschatellina. LEG: Göran Svensson,  Maja-Lena Nilsson,  Anna-Brita Carlander</t>
+          <t>Smålands flora 2007: KOO: 6F3e 1125. SOM: Trifolium montanum. LEG: Folke Jacobsson</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,7 +2079,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beteshage vid bäck</t>
+          <t>Hagmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2147,53 +2100,54 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73967111</t>
+          <t>https://artportalen.se/Sighting/75157951</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67558320</v>
+        <v>135164446</v>
       </c>
       <c r="B15" t="n">
-        <v>104641</v>
+        <v>107782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224416</v>
+        <v>221705</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Germunderyd, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520554</v>
+        <v>519987</v>
       </c>
       <c r="R15" t="n">
-        <v>6364402</v>
+        <v>6364423</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,12 +2171,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,7 +2202,661 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135164446</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4793801</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Germunderyd Torsgården, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>520928</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6364301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>F-Vet-0610</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4793801</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74268555</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99878</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Germunderyd Torsgården, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>520922</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6364296</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1989-06-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Carex pulicaris. LEG: Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74268555</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>109865542</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>520179</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6364511</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109865542</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73967111</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111018</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>28 Germunderyd S gdn 200 m VNV, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>520922</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6364296</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6F3e 1225. SOM: Adoxa moschatellina. LEG: Göran Svensson,  Maja-Lena Nilsson,  Anna-Brita Carlander</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Beteshage vid bäck</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73967111</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>67558320</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>520554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6364402</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/67558320</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135164415</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104806</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Germunderyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>519987</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6364423</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135164415</t>
         </is>
       </c>
     </row>
@@ -2268,6 +2876,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11238-2024 artfynd.xlsx
+++ b/artfynd/A 11238-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135163657</v>
       </c>
       <c r="B2" t="n">
-        <v>108036</v>
+        <v>108038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135164181</v>
       </c>
       <c r="B3" t="n">
-        <v>107780</v>
+        <v>107782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>135164666</v>
       </c>
       <c r="B5" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135164819</v>
       </c>
       <c r="B6" t="n">
-        <v>110035</v>
+        <v>110037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135164446</v>
       </c>
       <c r="B15" t="n">
-        <v>107782</v>
+        <v>107784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135164415</v>
       </c>
       <c r="B21" t="n">
-        <v>104806</v>
+        <v>104808</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
